--- a/CORTES DE CAJA/2026/3)MARZO/LISTA DE LAS VENTAS SEMANA 10 DE MARZO -26.xlsx
+++ b/CORTES DE CAJA/2026/3)MARZO/LISTA DE LAS VENTAS SEMANA 10 DE MARZO -26.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CECE2AED-E9A3-4D8B-A37D-148593880CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F318E2D7-49BE-44E5-A83F-5B79ED6219AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -738,7 +738,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">CUENTA DE HOY SABADO $ 2742 MENOS $ 300 PAGO DE YAS QUEDA $ 2442 MAS LO DE AYER EN CAJA $ 23260 
+      <t xml:space="preserve">CUENTA DE HOY SABADO $ 2752 MENOS $ 300 PAGO DE YAS QUEDA $ 2442 MAS LO DE AYER EN CAJA $ 23260 
 </t>
     </r>
     <r>
@@ -1132,6 +1132,27 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1171,26 +1192,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1200,9 +1203,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1791,23 +1791,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="34" t="s">
+      <c r="M2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -1820,14 +1820,14 @@
         <f>SUM(Tabla1[Importa])</f>
         <v>1110.5</v>
       </c>
-      <c r="M3" s="37" t="s">
+      <c r="M3" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="37"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="37"/>
-      <c r="R3" s="37"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
     </row>
     <row r="4" spans="2:18" ht="31.5" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -1858,17 +1858,17 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>12</v>
       </c>
-      <c r="M4" s="36"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C5">
         <f>IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -1887,21 +1887,21 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>12</v>
       </c>
-      <c r="J5" s="38" t="s">
+      <c r="J5" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="38"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
+      <c r="K5" s="25"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:C36" si="0">IF(ISNUMBER(E6), IF(ISNUMBER(C5), C5+1, 1), "")</f>
@@ -1920,19 +1920,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>171</v>
       </c>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -1954,19 +1954,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>235</v>
       </c>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="36"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -1988,19 +1988,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>63</v>
       </c>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="36"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -2022,19 +2022,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>81</v>
       </c>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -2053,19 +2053,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>42</v>
       </c>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="36"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -2084,19 +2084,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>108</v>
       </c>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -2115,19 +2115,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>15</v>
       </c>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -2149,19 +2149,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>111.5</v>
       </c>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -2183,19 +2183,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="J14" s="38"/>
-      <c r="K14" s="38"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="36"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="36"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -2217,17 +2217,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>164</v>
       </c>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="36"/>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="36"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -2249,12 +2249,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>63</v>
       </c>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="36"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18" t="str">
@@ -2269,12 +2269,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="36"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18" t="str">
@@ -2289,12 +2289,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="36"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18" t="str">
@@ -2309,12 +2309,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="36"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="23"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18" t="str">
@@ -2329,12 +2329,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M20" s="36"/>
-      <c r="N20" s="36"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="36"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
+      <c r="O20" s="23"/>
+      <c r="P20" s="23"/>
+      <c r="Q20" s="23"/>
+      <c r="R20" s="23"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18" t="str">
@@ -2349,12 +2349,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="36"/>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="36"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="23"/>
+      <c r="O21" s="23"/>
+      <c r="P21" s="23"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="str">
@@ -2369,12 +2369,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="36"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="str">
@@ -2403,14 +2403,14 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="32" t="s">
+      <c r="M24" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="32"/>
-      <c r="O24" s="32"/>
-      <c r="P24" s="32"/>
-      <c r="Q24" s="32"/>
-      <c r="R24" s="32"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
+      <c r="R24" s="19"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="str">
@@ -2425,12 +2425,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="33"/>
-      <c r="N25" s="33"/>
-      <c r="O25" s="33"/>
-      <c r="P25" s="33"/>
-      <c r="Q25" s="33"/>
-      <c r="R25" s="33"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
+      <c r="R25" s="20"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18" t="str">
@@ -2445,18 +2445,18 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G26))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M26" s="31" t="s">
+      <c r="M26" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="N26" s="31"/>
+      <c r="N26" s="38"/>
       <c r="O26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="P26" s="31" t="s">
+      <c r="P26" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B27" s="18" t="str">
@@ -2471,12 +2471,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G27))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M27" s="19"/>
-      <c r="N27" s="20"/>
-      <c r="O27" s="23"/>
-      <c r="P27" s="25"/>
-      <c r="Q27" s="26"/>
-      <c r="R27" s="27"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="27"/>
+      <c r="O27" s="30"/>
+      <c r="P27" s="32"/>
+      <c r="Q27" s="33"/>
+      <c r="R27" s="34"/>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="str">
@@ -2491,12 +2491,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G28))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M28" s="21"/>
-      <c r="N28" s="22"/>
-      <c r="O28" s="24"/>
-      <c r="P28" s="28"/>
-      <c r="Q28" s="29"/>
-      <c r="R28" s="30"/>
+      <c r="M28" s="28"/>
+      <c r="N28" s="29"/>
+      <c r="O28" s="31"/>
+      <c r="P28" s="35"/>
+      <c r="Q28" s="36"/>
+      <c r="R28" s="37"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="str">
@@ -2511,12 +2511,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G29))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M29" s="19"/>
-      <c r="N29" s="20"/>
-      <c r="O29" s="23"/>
-      <c r="P29" s="25"/>
-      <c r="Q29" s="26"/>
-      <c r="R29" s="27"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="27"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="32"/>
+      <c r="Q29" s="33"/>
+      <c r="R29" s="34"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -2531,12 +2531,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G30))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M30" s="21"/>
-      <c r="N30" s="22"/>
-      <c r="O30" s="24"/>
-      <c r="P30" s="28"/>
-      <c r="Q30" s="29"/>
-      <c r="R30" s="30"/>
+      <c r="M30" s="28"/>
+      <c r="N30" s="29"/>
+      <c r="O30" s="31"/>
+      <c r="P30" s="35"/>
+      <c r="Q30" s="36"/>
+      <c r="R30" s="37"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -2551,12 +2551,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G31))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M31" s="19"/>
-      <c r="N31" s="20"/>
-      <c r="O31" s="23"/>
-      <c r="P31" s="25"/>
-      <c r="Q31" s="26"/>
-      <c r="R31" s="27"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="27"/>
+      <c r="O31" s="30"/>
+      <c r="P31" s="32"/>
+      <c r="Q31" s="33"/>
+      <c r="R31" s="34"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -2571,12 +2571,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G32))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M32" s="21"/>
-      <c r="N32" s="22"/>
-      <c r="O32" s="24"/>
-      <c r="P32" s="28"/>
-      <c r="Q32" s="29"/>
-      <c r="R32" s="30"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="29"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="35"/>
+      <c r="Q32" s="36"/>
+      <c r="R32" s="37"/>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -2591,12 +2591,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G33))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M33" s="19"/>
-      <c r="N33" s="20"/>
-      <c r="O33" s="23"/>
-      <c r="P33" s="25"/>
-      <c r="Q33" s="26"/>
-      <c r="R33" s="27"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="27"/>
+      <c r="O33" s="30"/>
+      <c r="P33" s="32"/>
+      <c r="Q33" s="33"/>
+      <c r="R33" s="34"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -2611,12 +2611,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G34))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M34" s="21"/>
-      <c r="N34" s="22"/>
-      <c r="O34" s="24"/>
-      <c r="P34" s="28"/>
-      <c r="Q34" s="29"/>
-      <c r="R34" s="30"/>
+      <c r="M34" s="28"/>
+      <c r="N34" s="29"/>
+      <c r="O34" s="31"/>
+      <c r="P34" s="35"/>
+      <c r="Q34" s="36"/>
+      <c r="R34" s="37"/>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -2631,12 +2631,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G35))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M35" s="19"/>
-      <c r="N35" s="20"/>
-      <c r="O35" s="23"/>
-      <c r="P35" s="25"/>
-      <c r="Q35" s="26"/>
-      <c r="R35" s="27"/>
+      <c r="M35" s="26"/>
+      <c r="N35" s="27"/>
+      <c r="O35" s="30"/>
+      <c r="P35" s="32"/>
+      <c r="Q35" s="33"/>
+      <c r="R35" s="34"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -2651,12 +2651,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G36))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M36" s="21"/>
-      <c r="N36" s="22"/>
-      <c r="O36" s="24"/>
-      <c r="P36" s="28"/>
-      <c r="Q36" s="29"/>
-      <c r="R36" s="30"/>
+      <c r="M36" s="28"/>
+      <c r="N36" s="29"/>
+      <c r="O36" s="31"/>
+      <c r="P36" s="35"/>
+      <c r="Q36" s="36"/>
+      <c r="R36" s="37"/>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -2671,12 +2671,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G37))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M37" s="19"/>
-      <c r="N37" s="20"/>
-      <c r="O37" s="23"/>
-      <c r="P37" s="25"/>
-      <c r="Q37" s="26"/>
-      <c r="R37" s="27"/>
+      <c r="M37" s="26"/>
+      <c r="N37" s="27"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="32"/>
+      <c r="Q37" s="33"/>
+      <c r="R37" s="34"/>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -2691,12 +2691,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G38))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M38" s="21"/>
-      <c r="N38" s="22"/>
-      <c r="O38" s="24"/>
-      <c r="P38" s="28"/>
-      <c r="Q38" s="29"/>
-      <c r="R38" s="30"/>
+      <c r="M38" s="28"/>
+      <c r="N38" s="29"/>
+      <c r="O38" s="31"/>
+      <c r="P38" s="35"/>
+      <c r="Q38" s="36"/>
+      <c r="R38" s="37"/>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -2711,12 +2711,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G39))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M39" s="19"/>
-      <c r="N39" s="20"/>
-      <c r="O39" s="23"/>
-      <c r="P39" s="25"/>
-      <c r="Q39" s="26"/>
-      <c r="R39" s="27"/>
+      <c r="M39" s="26"/>
+      <c r="N39" s="27"/>
+      <c r="O39" s="30"/>
+      <c r="P39" s="32"/>
+      <c r="Q39" s="33"/>
+      <c r="R39" s="34"/>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -2731,12 +2731,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G40))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M40" s="21"/>
-      <c r="N40" s="22"/>
-      <c r="O40" s="24"/>
-      <c r="P40" s="28"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="30"/>
+      <c r="M40" s="28"/>
+      <c r="N40" s="29"/>
+      <c r="O40" s="31"/>
+      <c r="P40" s="35"/>
+      <c r="Q40" s="36"/>
+      <c r="R40" s="37"/>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -2751,12 +2751,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G41))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M41" s="19"/>
-      <c r="N41" s="20"/>
-      <c r="O41" s="23"/>
-      <c r="P41" s="25"/>
-      <c r="Q41" s="26"/>
-      <c r="R41" s="27"/>
+      <c r="M41" s="26"/>
+      <c r="N41" s="27"/>
+      <c r="O41" s="30"/>
+      <c r="P41" s="32"/>
+      <c r="Q41" s="33"/>
+      <c r="R41" s="34"/>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -2771,12 +2771,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G42))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M42" s="21"/>
-      <c r="N42" s="22"/>
-      <c r="O42" s="24"/>
-      <c r="P42" s="28"/>
-      <c r="Q42" s="29"/>
-      <c r="R42" s="30"/>
+      <c r="M42" s="28"/>
+      <c r="N42" s="29"/>
+      <c r="O42" s="31"/>
+      <c r="P42" s="35"/>
+      <c r="Q42" s="36"/>
+      <c r="R42" s="37"/>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -2791,12 +2791,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G43))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M43" s="19"/>
-      <c r="N43" s="20"/>
-      <c r="O43" s="23"/>
-      <c r="P43" s="25"/>
-      <c r="Q43" s="26"/>
-      <c r="R43" s="27"/>
+      <c r="M43" s="26"/>
+      <c r="N43" s="27"/>
+      <c r="O43" s="30"/>
+      <c r="P43" s="32"/>
+      <c r="Q43" s="33"/>
+      <c r="R43" s="34"/>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -2811,12 +2811,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G44))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M44" s="21"/>
-      <c r="N44" s="22"/>
-      <c r="O44" s="24"/>
-      <c r="P44" s="28"/>
-      <c r="Q44" s="29"/>
-      <c r="R44" s="30"/>
+      <c r="M44" s="28"/>
+      <c r="N44" s="29"/>
+      <c r="O44" s="31"/>
+      <c r="P44" s="35"/>
+      <c r="Q44" s="36"/>
+      <c r="R44" s="37"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -2831,12 +2831,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G45))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M45" s="19"/>
-      <c r="N45" s="20"/>
-      <c r="O45" s="23"/>
-      <c r="P45" s="25"/>
-      <c r="Q45" s="26"/>
-      <c r="R45" s="27"/>
+      <c r="M45" s="26"/>
+      <c r="N45" s="27"/>
+      <c r="O45" s="30"/>
+      <c r="P45" s="32"/>
+      <c r="Q45" s="33"/>
+      <c r="R45" s="34"/>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B46" s="18" t="str">
@@ -2851,12 +2851,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G46))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M46" s="21"/>
-      <c r="N46" s="22"/>
-      <c r="O46" s="24"/>
-      <c r="P46" s="28"/>
-      <c r="Q46" s="29"/>
-      <c r="R46" s="30"/>
+      <c r="M46" s="28"/>
+      <c r="N46" s="29"/>
+      <c r="O46" s="31"/>
+      <c r="P46" s="35"/>
+      <c r="Q46" s="36"/>
+      <c r="R46" s="37"/>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B47" s="18" t="str">
@@ -2871,12 +2871,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G47))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M47" s="19"/>
-      <c r="N47" s="20"/>
-      <c r="O47" s="23"/>
-      <c r="P47" s="25"/>
-      <c r="Q47" s="26"/>
-      <c r="R47" s="27"/>
+      <c r="M47" s="26"/>
+      <c r="N47" s="27"/>
+      <c r="O47" s="30"/>
+      <c r="P47" s="32"/>
+      <c r="Q47" s="33"/>
+      <c r="R47" s="34"/>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B48" s="18" t="str">
@@ -2891,12 +2891,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G48))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M48" s="21"/>
-      <c r="N48" s="22"/>
-      <c r="O48" s="24"/>
-      <c r="P48" s="28"/>
-      <c r="Q48" s="29"/>
-      <c r="R48" s="30"/>
+      <c r="M48" s="28"/>
+      <c r="N48" s="29"/>
+      <c r="O48" s="31"/>
+      <c r="P48" s="35"/>
+      <c r="Q48" s="36"/>
+      <c r="R48" s="37"/>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B49" s="18" t="str">
@@ -2911,12 +2911,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G49))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M49" s="19"/>
-      <c r="N49" s="20"/>
-      <c r="O49" s="23"/>
-      <c r="P49" s="25"/>
-      <c r="Q49" s="26"/>
-      <c r="R49" s="27"/>
+      <c r="M49" s="26"/>
+      <c r="N49" s="27"/>
+      <c r="O49" s="30"/>
+      <c r="P49" s="32"/>
+      <c r="Q49" s="33"/>
+      <c r="R49" s="34"/>
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B50" s="18" t="str">
@@ -2931,12 +2931,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G50))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M50" s="21"/>
-      <c r="N50" s="22"/>
-      <c r="O50" s="24"/>
-      <c r="P50" s="28"/>
-      <c r="Q50" s="29"/>
-      <c r="R50" s="30"/>
+      <c r="M50" s="28"/>
+      <c r="N50" s="29"/>
+      <c r="O50" s="31"/>
+      <c r="P50" s="35"/>
+      <c r="Q50" s="36"/>
+      <c r="R50" s="37"/>
     </row>
     <row r="51" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B51" s="18" t="str">
@@ -2951,12 +2951,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G51))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M51" s="19"/>
-      <c r="N51" s="20"/>
-      <c r="O51" s="23"/>
-      <c r="P51" s="25"/>
-      <c r="Q51" s="26"/>
-      <c r="R51" s="27"/>
+      <c r="M51" s="26"/>
+      <c r="N51" s="27"/>
+      <c r="O51" s="30"/>
+      <c r="P51" s="32"/>
+      <c r="Q51" s="33"/>
+      <c r="R51" s="34"/>
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B52" s="18" t="str">
@@ -2971,12 +2971,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G52))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M52" s="21"/>
-      <c r="N52" s="22"/>
-      <c r="O52" s="24"/>
-      <c r="P52" s="28"/>
-      <c r="Q52" s="29"/>
-      <c r="R52" s="30"/>
+      <c r="M52" s="28"/>
+      <c r="N52" s="29"/>
+      <c r="O52" s="31"/>
+      <c r="P52" s="35"/>
+      <c r="Q52" s="36"/>
+      <c r="R52" s="37"/>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B53" s="18" t="str">
@@ -3695,19 +3695,33 @@
   </sheetData>
   <autoFilter ref="B4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="48">
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="J5:K14"/>
-    <mergeCell ref="M41:N42"/>
-    <mergeCell ref="M43:N44"/>
-    <mergeCell ref="O41:O42"/>
-    <mergeCell ref="O43:O44"/>
-    <mergeCell ref="P41:R42"/>
-    <mergeCell ref="P43:R44"/>
+    <mergeCell ref="M49:N50"/>
+    <mergeCell ref="O49:O50"/>
+    <mergeCell ref="P49:R50"/>
+    <mergeCell ref="M51:N52"/>
+    <mergeCell ref="O51:O52"/>
+    <mergeCell ref="P51:R52"/>
+    <mergeCell ref="M45:N46"/>
+    <mergeCell ref="O45:O46"/>
+    <mergeCell ref="P45:R46"/>
+    <mergeCell ref="M47:N48"/>
+    <mergeCell ref="O47:O48"/>
+    <mergeCell ref="P47:R48"/>
+    <mergeCell ref="P31:R32"/>
+    <mergeCell ref="P33:R34"/>
+    <mergeCell ref="P35:R36"/>
+    <mergeCell ref="P37:R38"/>
+    <mergeCell ref="P39:R40"/>
+    <mergeCell ref="O31:O32"/>
+    <mergeCell ref="O33:O34"/>
+    <mergeCell ref="O35:O36"/>
+    <mergeCell ref="O37:O38"/>
+    <mergeCell ref="O39:O40"/>
+    <mergeCell ref="M31:N32"/>
+    <mergeCell ref="M33:N34"/>
+    <mergeCell ref="M35:N36"/>
+    <mergeCell ref="M37:N38"/>
+    <mergeCell ref="M39:N40"/>
     <mergeCell ref="P26:R26"/>
     <mergeCell ref="M26:N26"/>
     <mergeCell ref="M27:N28"/>
@@ -3716,33 +3730,19 @@
     <mergeCell ref="O29:O30"/>
     <mergeCell ref="P27:R28"/>
     <mergeCell ref="P29:R30"/>
-    <mergeCell ref="M31:N32"/>
-    <mergeCell ref="M33:N34"/>
-    <mergeCell ref="M35:N36"/>
-    <mergeCell ref="M37:N38"/>
-    <mergeCell ref="M39:N40"/>
-    <mergeCell ref="O31:O32"/>
-    <mergeCell ref="O33:O34"/>
-    <mergeCell ref="O35:O36"/>
-    <mergeCell ref="O37:O38"/>
-    <mergeCell ref="O39:O40"/>
-    <mergeCell ref="P31:R32"/>
-    <mergeCell ref="P33:R34"/>
-    <mergeCell ref="P35:R36"/>
-    <mergeCell ref="P37:R38"/>
-    <mergeCell ref="P39:R40"/>
-    <mergeCell ref="M45:N46"/>
-    <mergeCell ref="O45:O46"/>
-    <mergeCell ref="P45:R46"/>
-    <mergeCell ref="M47:N48"/>
-    <mergeCell ref="O47:O48"/>
-    <mergeCell ref="P47:R48"/>
-    <mergeCell ref="M49:N50"/>
-    <mergeCell ref="O49:O50"/>
-    <mergeCell ref="P49:R50"/>
-    <mergeCell ref="M51:N52"/>
-    <mergeCell ref="O51:O52"/>
-    <mergeCell ref="P51:R52"/>
+    <mergeCell ref="M41:N42"/>
+    <mergeCell ref="M43:N44"/>
+    <mergeCell ref="O41:O42"/>
+    <mergeCell ref="O43:O44"/>
+    <mergeCell ref="P41:R42"/>
+    <mergeCell ref="P43:R44"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="13" priority="1">
@@ -3782,23 +3782,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="34" t="s">
+      <c r="M2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -3811,14 +3811,14 @@
         <f>SUM(Tabla110[Importa])</f>
         <v>838</v>
       </c>
-      <c r="M3" s="37" t="s">
+      <c r="M3" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="37"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="37"/>
-      <c r="R3" s="37"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -3849,19 +3849,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>17</v>
       </c>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla110[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C68" si="0">IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -3880,21 +3880,21 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>12</v>
       </c>
-      <c r="J5" s="38" t="s">
+      <c r="J5" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="38"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
+      <c r="K5" s="25"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -3913,19 +3913,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>175</v>
       </c>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -3947,19 +3947,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>111.5</v>
       </c>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="36"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -3981,19 +3981,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>13.5</v>
       </c>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="36"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -4015,19 +4015,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -4049,19 +4049,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>76</v>
       </c>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="36"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -4083,19 +4083,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>31.5</v>
       </c>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -4114,19 +4114,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>135</v>
       </c>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -4148,19 +4148,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>27</v>
       </c>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -4182,19 +4182,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>18</v>
       </c>
-      <c r="J14" s="38"/>
-      <c r="K14" s="38"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="36"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="36"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -4213,17 +4213,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="36"/>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="36"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -4242,12 +4242,12 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>10</v>
       </c>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="36"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18" t="str">
@@ -4271,12 +4271,12 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>5</v>
       </c>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="36"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18" t="str">
@@ -4300,12 +4300,12 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>70</v>
       </c>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="36"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18" t="str">
@@ -4329,12 +4329,12 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>30</v>
       </c>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="36"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="23"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18" t="str">
@@ -4361,12 +4361,12 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>31.5</v>
       </c>
-      <c r="M20" s="36"/>
-      <c r="N20" s="36"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="36"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
+      <c r="O20" s="23"/>
+      <c r="P20" s="23"/>
+      <c r="Q20" s="23"/>
+      <c r="R20" s="23"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18" t="str">
@@ -4393,12 +4393,12 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>27</v>
       </c>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="36"/>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="36"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="23"/>
+      <c r="O21" s="23"/>
+      <c r="P21" s="23"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="str">
@@ -4413,12 +4413,12 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="36"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="str">
@@ -4447,14 +4447,14 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="32" t="s">
+      <c r="M24" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="42"/>
-      <c r="O24" s="42"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="42"/>
-      <c r="R24" s="42"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="39"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="str">
@@ -4469,12 +4469,12 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="37"/>
-      <c r="N25" s="37"/>
-      <c r="O25" s="37"/>
-      <c r="P25" s="37"/>
-      <c r="Q25" s="37"/>
-      <c r="R25" s="37"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="24"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B26" s="18" t="str">
@@ -4495,12 +4495,12 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="31" t="s">
+      <c r="O26" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
     </row>
     <row r="27" spans="2:18" ht="30" x14ac:dyDescent="0.25">
       <c r="B27" s="18" t="str">
@@ -4521,10 +4521,10 @@
       <c r="N27" s="15">
         <v>2141</v>
       </c>
-      <c r="O27" s="39"/>
-      <c r="P27" s="40"/>
-      <c r="Q27" s="40"/>
-      <c r="R27" s="41"/>
+      <c r="O27" s="40"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="42"/>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="str">
@@ -4541,10 +4541,10 @@
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="40"/>
-      <c r="Q28" s="40"/>
-      <c r="R28" s="41"/>
+      <c r="O28" s="40"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="42"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="str">
@@ -4561,10 +4561,10 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="40"/>
-      <c r="Q29" s="40"/>
-      <c r="R29" s="41"/>
+      <c r="O29" s="40"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="42"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -4581,10 +4581,10 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="40"/>
-      <c r="Q30" s="40"/>
-      <c r="R30" s="41"/>
+      <c r="O30" s="40"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="42"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -4601,10 +4601,10 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="39"/>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="40"/>
-      <c r="R31" s="41"/>
+      <c r="O31" s="40"/>
+      <c r="P31" s="41"/>
+      <c r="Q31" s="41"/>
+      <c r="R31" s="42"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -4621,10 +4621,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="39"/>
-      <c r="P32" s="40"/>
-      <c r="Q32" s="40"/>
-      <c r="R32" s="41"/>
+      <c r="O32" s="40"/>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="41"/>
+      <c r="R32" s="42"/>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -4641,10 +4641,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="39"/>
-      <c r="P33" s="40"/>
-      <c r="Q33" s="40"/>
-      <c r="R33" s="41"/>
+      <c r="O33" s="40"/>
+      <c r="P33" s="41"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="42"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -4661,10 +4661,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="39"/>
-      <c r="P34" s="40"/>
-      <c r="Q34" s="40"/>
-      <c r="R34" s="41"/>
+      <c r="O34" s="40"/>
+      <c r="P34" s="41"/>
+      <c r="Q34" s="41"/>
+      <c r="R34" s="42"/>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -4681,10 +4681,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="39"/>
-      <c r="P35" s="40"/>
-      <c r="Q35" s="40"/>
-      <c r="R35" s="41"/>
+      <c r="O35" s="40"/>
+      <c r="P35" s="41"/>
+      <c r="Q35" s="41"/>
+      <c r="R35" s="42"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -4701,10 +4701,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="39"/>
-      <c r="P36" s="40"/>
-      <c r="Q36" s="40"/>
-      <c r="R36" s="41"/>
+      <c r="O36" s="40"/>
+      <c r="P36" s="41"/>
+      <c r="Q36" s="41"/>
+      <c r="R36" s="42"/>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -4721,10 +4721,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="39"/>
-      <c r="P37" s="40"/>
-      <c r="Q37" s="40"/>
-      <c r="R37" s="41"/>
+      <c r="O37" s="40"/>
+      <c r="P37" s="41"/>
+      <c r="Q37" s="41"/>
+      <c r="R37" s="42"/>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -4741,10 +4741,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="39"/>
-      <c r="P38" s="40"/>
-      <c r="Q38" s="40"/>
-      <c r="R38" s="41"/>
+      <c r="O38" s="40"/>
+      <c r="P38" s="41"/>
+      <c r="Q38" s="41"/>
+      <c r="R38" s="42"/>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -4761,10 +4761,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="39"/>
-      <c r="P39" s="40"/>
-      <c r="Q39" s="40"/>
-      <c r="R39" s="41"/>
+      <c r="O39" s="40"/>
+      <c r="P39" s="41"/>
+      <c r="Q39" s="41"/>
+      <c r="R39" s="42"/>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -4781,10 +4781,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="39"/>
-      <c r="P40" s="40"/>
-      <c r="Q40" s="40"/>
-      <c r="R40" s="41"/>
+      <c r="O40" s="40"/>
+      <c r="P40" s="41"/>
+      <c r="Q40" s="41"/>
+      <c r="R40" s="42"/>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -4801,10 +4801,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="40"/>
-      <c r="Q41" s="40"/>
-      <c r="R41" s="41"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="41"/>
+      <c r="Q41" s="41"/>
+      <c r="R41" s="42"/>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -4821,10 +4821,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="39"/>
-      <c r="P42" s="40"/>
-      <c r="Q42" s="40"/>
-      <c r="R42" s="41"/>
+      <c r="O42" s="40"/>
+      <c r="P42" s="41"/>
+      <c r="Q42" s="41"/>
+      <c r="R42" s="42"/>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -4841,10 +4841,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="39"/>
-      <c r="P43" s="40"/>
-      <c r="Q43" s="40"/>
-      <c r="R43" s="41"/>
+      <c r="O43" s="40"/>
+      <c r="P43" s="41"/>
+      <c r="Q43" s="41"/>
+      <c r="R43" s="42"/>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -4861,10 +4861,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="39"/>
-      <c r="P44" s="40"/>
-      <c r="Q44" s="40"/>
-      <c r="R44" s="41"/>
+      <c r="O44" s="40"/>
+      <c r="P44" s="41"/>
+      <c r="Q44" s="41"/>
+      <c r="R44" s="42"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -5694,32 +5694,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -5758,23 +5758,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="34" t="s">
+      <c r="M2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -5787,14 +5787,14 @@
         <f>SUM(Tabla111[Importa])</f>
         <v>553</v>
       </c>
-      <c r="M3" s="37" t="s">
+      <c r="M3" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="37"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="37"/>
-      <c r="R3" s="37"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -5825,19 +5825,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>11</v>
       </c>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla111[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C5">
         <f>IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -5856,21 +5856,21 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>80</v>
       </c>
-      <c r="J5" s="38" t="s">
+      <c r="J5" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="38"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
+      <c r="K5" s="25"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6" si="0">IF(ISNUMBER(E6), IF(ISNUMBER(C5), C5+1, 1), "")</f>
@@ -5892,19 +5892,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>34.5</v>
       </c>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C7">
         <f>IF(ISNUMBER(E7), IF(ISNUMBER(C6), C6+1, 1), "")</f>
@@ -5926,19 +5926,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>13.5</v>
       </c>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="36"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C68" si="1">IF(ISNUMBER(E8), IF(ISNUMBER(C7), C7+1, 1), "")</f>
@@ -5957,19 +5957,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="36"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
@@ -5991,19 +5991,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>54</v>
       </c>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
@@ -6022,19 +6022,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>190</v>
       </c>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="36"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
@@ -6053,19 +6053,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>10</v>
       </c>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
@@ -6084,19 +6084,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>9</v>
       </c>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
@@ -6115,19 +6115,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>87</v>
       </c>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
@@ -6146,19 +6146,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>5</v>
       </c>
-      <c r="J14" s="38"/>
-      <c r="K14" s="38"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="36"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="36"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C15">
         <f t="shared" si="1"/>
@@ -6177,17 +6177,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>50</v>
       </c>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="36"/>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="36"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C16" t="str">
         <f t="shared" si="1"/>
@@ -6197,12 +6197,12 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="36"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18" t="str">
@@ -6217,12 +6217,12 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="36"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18" t="str">
@@ -6237,12 +6237,12 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="36"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18" t="str">
@@ -6257,12 +6257,12 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="36"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="23"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18" t="str">
@@ -6277,12 +6277,12 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M20" s="36"/>
-      <c r="N20" s="36"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="36"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
+      <c r="O20" s="23"/>
+      <c r="P20" s="23"/>
+      <c r="Q20" s="23"/>
+      <c r="R20" s="23"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18" t="str">
@@ -6297,12 +6297,12 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="36"/>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="36"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="23"/>
+      <c r="O21" s="23"/>
+      <c r="P21" s="23"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="str">
@@ -6317,12 +6317,12 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="36"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="str">
@@ -6351,14 +6351,14 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="32" t="s">
+      <c r="M24" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="42"/>
-      <c r="O24" s="42"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="42"/>
-      <c r="R24" s="42"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="39"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="str">
@@ -6373,12 +6373,12 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="37"/>
-      <c r="N25" s="37"/>
-      <c r="O25" s="37"/>
-      <c r="P25" s="37"/>
-      <c r="Q25" s="37"/>
-      <c r="R25" s="37"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="24"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18" t="str">
@@ -6399,12 +6399,12 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="31" t="s">
+      <c r="O26" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
     </row>
     <row r="27" spans="2:18" ht="45" x14ac:dyDescent="0.25">
       <c r="B27" s="18" t="str">
@@ -6425,10 +6425,10 @@
       <c r="N27" s="15">
         <v>69</v>
       </c>
-      <c r="O27" s="39"/>
-      <c r="P27" s="40"/>
-      <c r="Q27" s="40"/>
-      <c r="R27" s="41"/>
+      <c r="O27" s="40"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="42"/>
     </row>
     <row r="28" spans="2:18" ht="45" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="str">
@@ -6449,10 +6449,10 @@
       <c r="N28" s="15">
         <v>4286</v>
       </c>
-      <c r="O28" s="39"/>
-      <c r="P28" s="40"/>
-      <c r="Q28" s="40"/>
-      <c r="R28" s="41"/>
+      <c r="O28" s="40"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="42"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="str">
@@ -6469,10 +6469,10 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="40"/>
-      <c r="Q29" s="40"/>
-      <c r="R29" s="41"/>
+      <c r="O29" s="40"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="42"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -6489,10 +6489,10 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="40"/>
-      <c r="Q30" s="40"/>
-      <c r="R30" s="41"/>
+      <c r="O30" s="40"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="42"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -6509,10 +6509,10 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="39"/>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="40"/>
-      <c r="R31" s="41"/>
+      <c r="O31" s="40"/>
+      <c r="P31" s="41"/>
+      <c r="Q31" s="41"/>
+      <c r="R31" s="42"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -6529,10 +6529,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="39"/>
-      <c r="P32" s="40"/>
-      <c r="Q32" s="40"/>
-      <c r="R32" s="41"/>
+      <c r="O32" s="40"/>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="41"/>
+      <c r="R32" s="42"/>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -6549,10 +6549,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="39"/>
-      <c r="P33" s="40"/>
-      <c r="Q33" s="40"/>
-      <c r="R33" s="41"/>
+      <c r="O33" s="40"/>
+      <c r="P33" s="41"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="42"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -6569,10 +6569,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="39"/>
-      <c r="P34" s="40"/>
-      <c r="Q34" s="40"/>
-      <c r="R34" s="41"/>
+      <c r="O34" s="40"/>
+      <c r="P34" s="41"/>
+      <c r="Q34" s="41"/>
+      <c r="R34" s="42"/>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -6589,10 +6589,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="39"/>
-      <c r="P35" s="40"/>
-      <c r="Q35" s="40"/>
-      <c r="R35" s="41"/>
+      <c r="O35" s="40"/>
+      <c r="P35" s="41"/>
+      <c r="Q35" s="41"/>
+      <c r="R35" s="42"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -6609,10 +6609,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="39"/>
-      <c r="P36" s="40"/>
-      <c r="Q36" s="40"/>
-      <c r="R36" s="41"/>
+      <c r="O36" s="40"/>
+      <c r="P36" s="41"/>
+      <c r="Q36" s="41"/>
+      <c r="R36" s="42"/>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -6629,10 +6629,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="39"/>
-      <c r="P37" s="40"/>
-      <c r="Q37" s="40"/>
-      <c r="R37" s="41"/>
+      <c r="O37" s="40"/>
+      <c r="P37" s="41"/>
+      <c r="Q37" s="41"/>
+      <c r="R37" s="42"/>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -6649,10 +6649,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="39"/>
-      <c r="P38" s="40"/>
-      <c r="Q38" s="40"/>
-      <c r="R38" s="41"/>
+      <c r="O38" s="40"/>
+      <c r="P38" s="41"/>
+      <c r="Q38" s="41"/>
+      <c r="R38" s="42"/>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -6669,10 +6669,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="39"/>
-      <c r="P39" s="40"/>
-      <c r="Q39" s="40"/>
-      <c r="R39" s="41"/>
+      <c r="O39" s="40"/>
+      <c r="P39" s="41"/>
+      <c r="Q39" s="41"/>
+      <c r="R39" s="42"/>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -6689,10 +6689,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="39"/>
-      <c r="P40" s="40"/>
-      <c r="Q40" s="40"/>
-      <c r="R40" s="41"/>
+      <c r="O40" s="40"/>
+      <c r="P40" s="41"/>
+      <c r="Q40" s="41"/>
+      <c r="R40" s="42"/>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -6709,10 +6709,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="40"/>
-      <c r="Q41" s="40"/>
-      <c r="R41" s="41"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="41"/>
+      <c r="Q41" s="41"/>
+      <c r="R41" s="42"/>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -6729,10 +6729,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="39"/>
-      <c r="P42" s="40"/>
-      <c r="Q42" s="40"/>
-      <c r="R42" s="41"/>
+      <c r="O42" s="40"/>
+      <c r="P42" s="41"/>
+      <c r="Q42" s="41"/>
+      <c r="R42" s="42"/>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -6749,10 +6749,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="39"/>
-      <c r="P43" s="40"/>
-      <c r="Q43" s="40"/>
-      <c r="R43" s="41"/>
+      <c r="O43" s="40"/>
+      <c r="P43" s="41"/>
+      <c r="Q43" s="41"/>
+      <c r="R43" s="42"/>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -6769,10 +6769,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="39"/>
-      <c r="P44" s="40"/>
-      <c r="Q44" s="40"/>
-      <c r="R44" s="41"/>
+      <c r="O44" s="40"/>
+      <c r="P44" s="41"/>
+      <c r="Q44" s="41"/>
+      <c r="R44" s="42"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -7602,32 +7602,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="9" priority="1">
@@ -7665,23 +7665,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="34" t="s">
+      <c r="M2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -7694,14 +7694,14 @@
         <f>SUM(Tabla112[Importa])</f>
         <v>1641.5</v>
       </c>
-      <c r="M3" s="37" t="s">
+      <c r="M3" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="37"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="37"/>
-      <c r="R3" s="37"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -7732,17 +7732,17 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>11</v>
       </c>
-      <c r="M4" s="36"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla112[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C68" si="0">IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -7764,21 +7764,21 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>75</v>
       </c>
-      <c r="J5" s="38" t="s">
+      <c r="J5" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="38"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
+      <c r="K5" s="25"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -7797,19 +7797,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>2</v>
       </c>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -7831,19 +7831,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>225</v>
       </c>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="36"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -7865,19 +7865,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>180</v>
       </c>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="36"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -7896,19 +7896,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>180</v>
       </c>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -7927,19 +7927,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>35</v>
       </c>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="36"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -7961,19 +7961,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>252</v>
       </c>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -7995,19 +7995,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>252</v>
       </c>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -8029,19 +8029,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>288</v>
       </c>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -8063,19 +8063,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>72</v>
       </c>
-      <c r="J14" s="38"/>
-      <c r="K14" s="38"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="36"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="36"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -8097,17 +8097,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>80.5</v>
       </c>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="36"/>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="36"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C16" t="str">
         <f t="shared" si="0"/>
@@ -8117,12 +8117,12 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="36"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18" t="str">
@@ -8137,12 +8137,12 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="36"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18" t="str">
@@ -8157,12 +8157,12 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="36"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18" t="str">
@@ -8177,12 +8177,12 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="36"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="23"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18" t="str">
@@ -8197,12 +8197,12 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M20" s="36"/>
-      <c r="N20" s="36"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="36"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
+      <c r="O20" s="23"/>
+      <c r="P20" s="23"/>
+      <c r="Q20" s="23"/>
+      <c r="R20" s="23"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18" t="str">
@@ -8217,12 +8217,12 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="36"/>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="36"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="23"/>
+      <c r="O21" s="23"/>
+      <c r="P21" s="23"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="str">
@@ -8237,12 +8237,12 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="36"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="str">
@@ -8271,14 +8271,14 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="32" t="s">
+      <c r="M24" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="42"/>
-      <c r="O24" s="42"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="42"/>
-      <c r="R24" s="42"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="39"/>
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="str">
@@ -8293,12 +8293,12 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="37"/>
-      <c r="N25" s="37"/>
-      <c r="O25" s="37"/>
-      <c r="P25" s="37"/>
-      <c r="Q25" s="37"/>
-      <c r="R25" s="37"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="24"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18" t="str">
@@ -8319,12 +8319,12 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="31" t="s">
+      <c r="O26" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
     </row>
     <row r="27" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18" t="str">
@@ -8341,10 +8341,10 @@
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="15"/>
-      <c r="O27" s="39"/>
-      <c r="P27" s="40"/>
-      <c r="Q27" s="40"/>
-      <c r="R27" s="41"/>
+      <c r="O27" s="40"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="42"/>
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="str">
@@ -8361,10 +8361,10 @@
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="40"/>
-      <c r="Q28" s="40"/>
-      <c r="R28" s="41"/>
+      <c r="O28" s="40"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="42"/>
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="str">
@@ -8381,10 +8381,10 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="40"/>
-      <c r="Q29" s="40"/>
-      <c r="R29" s="41"/>
+      <c r="O29" s="40"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="42"/>
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -8401,10 +8401,10 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="40"/>
-      <c r="Q30" s="40"/>
-      <c r="R30" s="41"/>
+      <c r="O30" s="40"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="42"/>
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -8421,10 +8421,10 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="39"/>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="40"/>
-      <c r="R31" s="41"/>
+      <c r="O31" s="40"/>
+      <c r="P31" s="41"/>
+      <c r="Q31" s="41"/>
+      <c r="R31" s="42"/>
     </row>
     <row r="32" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -8441,10 +8441,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="39"/>
-      <c r="P32" s="40"/>
-      <c r="Q32" s="40"/>
-      <c r="R32" s="41"/>
+      <c r="O32" s="40"/>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="41"/>
+      <c r="R32" s="42"/>
     </row>
     <row r="33" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -8461,10 +8461,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="39"/>
-      <c r="P33" s="40"/>
-      <c r="Q33" s="40"/>
-      <c r="R33" s="41"/>
+      <c r="O33" s="40"/>
+      <c r="P33" s="41"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="42"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -8481,10 +8481,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="39"/>
-      <c r="P34" s="40"/>
-      <c r="Q34" s="40"/>
-      <c r="R34" s="41"/>
+      <c r="O34" s="40"/>
+      <c r="P34" s="41"/>
+      <c r="Q34" s="41"/>
+      <c r="R34" s="42"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -8501,10 +8501,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="39"/>
-      <c r="P35" s="40"/>
-      <c r="Q35" s="40"/>
-      <c r="R35" s="41"/>
+      <c r="O35" s="40"/>
+      <c r="P35" s="41"/>
+      <c r="Q35" s="41"/>
+      <c r="R35" s="42"/>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -8521,10 +8521,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="39"/>
-      <c r="P36" s="40"/>
-      <c r="Q36" s="40"/>
-      <c r="R36" s="41"/>
+      <c r="O36" s="40"/>
+      <c r="P36" s="41"/>
+      <c r="Q36" s="41"/>
+      <c r="R36" s="42"/>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -8541,10 +8541,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="39"/>
-      <c r="P37" s="40"/>
-      <c r="Q37" s="40"/>
-      <c r="R37" s="41"/>
+      <c r="O37" s="40"/>
+      <c r="P37" s="41"/>
+      <c r="Q37" s="41"/>
+      <c r="R37" s="42"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -8561,10 +8561,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="39"/>
-      <c r="P38" s="40"/>
-      <c r="Q38" s="40"/>
-      <c r="R38" s="41"/>
+      <c r="O38" s="40"/>
+      <c r="P38" s="41"/>
+      <c r="Q38" s="41"/>
+      <c r="R38" s="42"/>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -8581,10 +8581,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="39"/>
-      <c r="P39" s="40"/>
-      <c r="Q39" s="40"/>
-      <c r="R39" s="41"/>
+      <c r="O39" s="40"/>
+      <c r="P39" s="41"/>
+      <c r="Q39" s="41"/>
+      <c r="R39" s="42"/>
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -8601,10 +8601,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="39"/>
-      <c r="P40" s="40"/>
-      <c r="Q40" s="40"/>
-      <c r="R40" s="41"/>
+      <c r="O40" s="40"/>
+      <c r="P40" s="41"/>
+      <c r="Q40" s="41"/>
+      <c r="R40" s="42"/>
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -8621,10 +8621,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="40"/>
-      <c r="Q41" s="40"/>
-      <c r="R41" s="41"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="41"/>
+      <c r="Q41" s="41"/>
+      <c r="R41" s="42"/>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -8641,10 +8641,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="39"/>
-      <c r="P42" s="40"/>
-      <c r="Q42" s="40"/>
-      <c r="R42" s="41"/>
+      <c r="O42" s="40"/>
+      <c r="P42" s="41"/>
+      <c r="Q42" s="41"/>
+      <c r="R42" s="42"/>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -8661,10 +8661,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="39"/>
-      <c r="P43" s="40"/>
-      <c r="Q43" s="40"/>
-      <c r="R43" s="41"/>
+      <c r="O43" s="40"/>
+      <c r="P43" s="41"/>
+      <c r="Q43" s="41"/>
+      <c r="R43" s="42"/>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -8681,10 +8681,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="39"/>
-      <c r="P44" s="40"/>
-      <c r="Q44" s="40"/>
-      <c r="R44" s="41"/>
+      <c r="O44" s="40"/>
+      <c r="P44" s="41"/>
+      <c r="Q44" s="41"/>
+      <c r="R44" s="42"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -9514,32 +9514,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="7" priority="1">
@@ -9578,23 +9578,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="34" t="s">
+      <c r="M2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -9607,14 +9607,14 @@
         <f>SUM(Tabla113[Importa])</f>
         <v>2448</v>
       </c>
-      <c r="M3" s="37" t="s">
+      <c r="M3" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="37"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="37"/>
-      <c r="R3" s="37"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -9645,14 +9645,14 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>24</v>
       </c>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18" t="str">
@@ -9667,21 +9667,21 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J5" s="38" t="s">
+      <c r="J5" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="38"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
+      <c r="K5" s="25"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -9703,19 +9703,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>75</v>
       </c>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -9734,19 +9734,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>110</v>
       </c>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="36"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -9765,19 +9765,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>95</v>
       </c>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="36"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -9796,19 +9796,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>12</v>
       </c>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -9827,19 +9827,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>380</v>
       </c>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="36"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -9861,19 +9861,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>142.5</v>
       </c>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -9895,19 +9895,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>18</v>
       </c>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -9929,19 +9929,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>222.5</v>
       </c>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -9963,19 +9963,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>90</v>
       </c>
-      <c r="J14" s="38"/>
-      <c r="K14" s="38"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="36"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="36"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -9997,17 +9997,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>27</v>
       </c>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="36"/>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="36"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -10029,12 +10029,12 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>64</v>
       </c>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="36"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18" t="str">
@@ -10061,12 +10061,12 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>59.5</v>
       </c>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="36"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18" t="str">
@@ -10093,12 +10093,12 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>32.5</v>
       </c>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="36"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18" t="str">
@@ -10125,12 +10125,12 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="36"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="23"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18" t="str">
@@ -10157,12 +10157,12 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>111.5</v>
       </c>
-      <c r="M20" s="36"/>
-      <c r="N20" s="36"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="36"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
+      <c r="O20" s="23"/>
+      <c r="P20" s="23"/>
+      <c r="Q20" s="23"/>
+      <c r="R20" s="23"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18" t="str">
@@ -10189,12 +10189,12 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>111.5</v>
       </c>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="36"/>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="36"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="23"/>
+      <c r="O21" s="23"/>
+      <c r="P21" s="23"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="str">
@@ -10221,12 +10221,12 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="36"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="str">
@@ -10279,14 +10279,14 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>229.5</v>
       </c>
-      <c r="M24" s="32" t="s">
+      <c r="M24" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="42"/>
-      <c r="O24" s="42"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="42"/>
-      <c r="R24" s="42"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="39"/>
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="str">
@@ -10313,12 +10313,12 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>135</v>
       </c>
-      <c r="M25" s="37"/>
-      <c r="N25" s="37"/>
-      <c r="O25" s="37"/>
-      <c r="P25" s="37"/>
-      <c r="Q25" s="37"/>
-      <c r="R25" s="37"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="24"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18" t="str">
@@ -10351,12 +10351,12 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="31" t="s">
+      <c r="O26" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
     </row>
     <row r="27" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18" t="str">
@@ -10389,12 +10389,12 @@
       <c r="N27" s="15">
         <v>2141</v>
       </c>
-      <c r="O27" s="39" t="s">
+      <c r="O27" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="P27" s="40"/>
-      <c r="Q27" s="40"/>
-      <c r="R27" s="41"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="42"/>
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="str">
@@ -10424,12 +10424,12 @@
       <c r="N28" s="15">
         <v>69</v>
       </c>
-      <c r="O28" s="39" t="s">
+      <c r="O28" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="P28" s="40"/>
-      <c r="Q28" s="40"/>
-      <c r="R28" s="41"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="42"/>
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="str">
@@ -10462,12 +10462,12 @@
       <c r="N29" s="15">
         <v>4286</v>
       </c>
-      <c r="O29" s="39" t="s">
+      <c r="O29" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="P29" s="40"/>
-      <c r="Q29" s="40"/>
-      <c r="R29" s="41"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="42"/>
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -10488,12 +10488,12 @@
       <c r="N30" s="15">
         <v>80</v>
       </c>
-      <c r="O30" s="39" t="s">
+      <c r="O30" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="P30" s="40"/>
-      <c r="Q30" s="40"/>
-      <c r="R30" s="41"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="42"/>
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -10514,12 +10514,12 @@
       <c r="N31" s="15">
         <v>1500</v>
       </c>
-      <c r="O31" s="39" t="s">
+      <c r="O31" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="40"/>
-      <c r="R31" s="41"/>
+      <c r="P31" s="41"/>
+      <c r="Q31" s="41"/>
+      <c r="R31" s="42"/>
     </row>
     <row r="32" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -10540,12 +10540,12 @@
       <c r="N32" s="15">
         <v>8076</v>
       </c>
-      <c r="O32" s="39" t="s">
+      <c r="O32" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="P32" s="40"/>
-      <c r="Q32" s="40"/>
-      <c r="R32" s="41"/>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="41"/>
+      <c r="R32" s="42"/>
     </row>
     <row r="33" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -10562,10 +10562,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="39"/>
-      <c r="P33" s="40"/>
-      <c r="Q33" s="40"/>
-      <c r="R33" s="41"/>
+      <c r="O33" s="40"/>
+      <c r="P33" s="41"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="42"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -10582,10 +10582,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="39"/>
-      <c r="P34" s="40"/>
-      <c r="Q34" s="40"/>
-      <c r="R34" s="41"/>
+      <c r="O34" s="40"/>
+      <c r="P34" s="41"/>
+      <c r="Q34" s="41"/>
+      <c r="R34" s="42"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -10602,10 +10602,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="39"/>
-      <c r="P35" s="40"/>
-      <c r="Q35" s="40"/>
-      <c r="R35" s="41"/>
+      <c r="O35" s="40"/>
+      <c r="P35" s="41"/>
+      <c r="Q35" s="41"/>
+      <c r="R35" s="42"/>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -10622,10 +10622,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="39"/>
-      <c r="P36" s="40"/>
-      <c r="Q36" s="40"/>
-      <c r="R36" s="41"/>
+      <c r="O36" s="40"/>
+      <c r="P36" s="41"/>
+      <c r="Q36" s="41"/>
+      <c r="R36" s="42"/>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -10642,10 +10642,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="39"/>
-      <c r="P37" s="40"/>
-      <c r="Q37" s="40"/>
-      <c r="R37" s="41"/>
+      <c r="O37" s="40"/>
+      <c r="P37" s="41"/>
+      <c r="Q37" s="41"/>
+      <c r="R37" s="42"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -10662,10 +10662,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="39"/>
-      <c r="P38" s="40"/>
-      <c r="Q38" s="40"/>
-      <c r="R38" s="41"/>
+      <c r="O38" s="40"/>
+      <c r="P38" s="41"/>
+      <c r="Q38" s="41"/>
+      <c r="R38" s="42"/>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -10682,10 +10682,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="39"/>
-      <c r="P39" s="40"/>
-      <c r="Q39" s="40"/>
-      <c r="R39" s="41"/>
+      <c r="O39" s="40"/>
+      <c r="P39" s="41"/>
+      <c r="Q39" s="41"/>
+      <c r="R39" s="42"/>
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -10702,10 +10702,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="39"/>
-      <c r="P40" s="40"/>
-      <c r="Q40" s="40"/>
-      <c r="R40" s="41"/>
+      <c r="O40" s="40"/>
+      <c r="P40" s="41"/>
+      <c r="Q40" s="41"/>
+      <c r="R40" s="42"/>
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -10722,10 +10722,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="40"/>
-      <c r="Q41" s="40"/>
-      <c r="R41" s="41"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="41"/>
+      <c r="Q41" s="41"/>
+      <c r="R41" s="42"/>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -10742,10 +10742,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="39"/>
-      <c r="P42" s="40"/>
-      <c r="Q42" s="40"/>
-      <c r="R42" s="41"/>
+      <c r="O42" s="40"/>
+      <c r="P42" s="41"/>
+      <c r="Q42" s="41"/>
+      <c r="R42" s="42"/>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -10762,10 +10762,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="39"/>
-      <c r="P43" s="40"/>
-      <c r="Q43" s="40"/>
-      <c r="R43" s="41"/>
+      <c r="O43" s="40"/>
+      <c r="P43" s="41"/>
+      <c r="Q43" s="41"/>
+      <c r="R43" s="42"/>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -10782,10 +10782,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="39"/>
-      <c r="P44" s="40"/>
-      <c r="Q44" s="40"/>
-      <c r="R44" s="41"/>
+      <c r="O44" s="40"/>
+      <c r="P44" s="41"/>
+      <c r="Q44" s="41"/>
+      <c r="R44" s="42"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -11615,32 +11615,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11678,23 +11678,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="34" t="s">
+      <c r="M2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -11707,14 +11707,14 @@
         <f>SUM(Tabla114[Importa])</f>
         <v>2752</v>
       </c>
-      <c r="M3" s="37" t="s">
+      <c r="M3" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="37"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="37"/>
-      <c r="R3" s="37"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -11745,19 +11745,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>16</v>
       </c>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla114[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C68" si="0">IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -11776,21 +11776,21 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>130</v>
       </c>
-      <c r="J5" s="38" t="s">
+      <c r="J5" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="38"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
+      <c r="K5" s="25"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -11809,19 +11809,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>172</v>
       </c>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -11840,19 +11840,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>72</v>
       </c>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="36"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -11871,19 +11871,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>10</v>
       </c>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="36"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -11902,19 +11902,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>12</v>
       </c>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -11933,19 +11933,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>5</v>
       </c>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="36"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -11967,19 +11967,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>49.5</v>
       </c>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -11998,19 +11998,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>60</v>
       </c>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -12029,19 +12029,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>77</v>
       </c>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -12060,19 +12060,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>40</v>
       </c>
-      <c r="J14" s="38"/>
-      <c r="K14" s="38"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="36"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="36"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -12091,17 +12091,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>15</v>
       </c>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="36"/>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="36"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -12120,12 +12120,12 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>25</v>
       </c>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="36"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18" t="str">
@@ -12149,12 +12149,12 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>325</v>
       </c>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="36"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18" t="str">
@@ -12181,12 +12181,12 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>449.5</v>
       </c>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="36"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18" t="str">
@@ -12210,12 +12210,12 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>10</v>
       </c>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="36"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="23"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18" t="str">
@@ -12239,12 +12239,12 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>1300</v>
       </c>
-      <c r="M20" s="36"/>
-      <c r="N20" s="36"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="36"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
+      <c r="O20" s="23"/>
+      <c r="P20" s="23"/>
+      <c r="Q20" s="23"/>
+      <c r="R20" s="23"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18" t="str">
@@ -12259,12 +12259,12 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="36"/>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="36"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="23"/>
+      <c r="O21" s="23"/>
+      <c r="P21" s="23"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="str">
@@ -12279,12 +12279,12 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="36"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="str">
@@ -12313,14 +12313,14 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="32" t="s">
+      <c r="M24" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="42"/>
-      <c r="O24" s="42"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="42"/>
-      <c r="R24" s="42"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="39"/>
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="str">
@@ -12335,12 +12335,12 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="37"/>
-      <c r="N25" s="37"/>
-      <c r="O25" s="37"/>
-      <c r="P25" s="37"/>
-      <c r="Q25" s="37"/>
-      <c r="R25" s="37"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="24"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18" t="str">
@@ -12361,12 +12361,12 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="31" t="s">
+      <c r="O26" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
     </row>
     <row r="27" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18" t="str">
@@ -12383,10 +12383,10 @@
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="15"/>
-      <c r="O27" s="39"/>
-      <c r="P27" s="40"/>
-      <c r="Q27" s="40"/>
-      <c r="R27" s="41"/>
+      <c r="O27" s="40"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="42"/>
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="str">
@@ -12403,10 +12403,10 @@
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="40"/>
-      <c r="Q28" s="40"/>
-      <c r="R28" s="41"/>
+      <c r="O28" s="40"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="42"/>
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="str">
@@ -12423,10 +12423,10 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="40"/>
-      <c r="Q29" s="40"/>
-      <c r="R29" s="41"/>
+      <c r="O29" s="40"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="42"/>
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -12443,10 +12443,10 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="40"/>
-      <c r="Q30" s="40"/>
-      <c r="R30" s="41"/>
+      <c r="O30" s="40"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="42"/>
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -12463,10 +12463,10 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="39"/>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="40"/>
-      <c r="R31" s="41"/>
+      <c r="O31" s="40"/>
+      <c r="P31" s="41"/>
+      <c r="Q31" s="41"/>
+      <c r="R31" s="42"/>
     </row>
     <row r="32" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -12483,10 +12483,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="39"/>
-      <c r="P32" s="40"/>
-      <c r="Q32" s="40"/>
-      <c r="R32" s="41"/>
+      <c r="O32" s="40"/>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="41"/>
+      <c r="R32" s="42"/>
     </row>
     <row r="33" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -12503,10 +12503,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="39"/>
-      <c r="P33" s="40"/>
-      <c r="Q33" s="40"/>
-      <c r="R33" s="41"/>
+      <c r="O33" s="40"/>
+      <c r="P33" s="41"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="42"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -12523,10 +12523,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="39"/>
-      <c r="P34" s="40"/>
-      <c r="Q34" s="40"/>
-      <c r="R34" s="41"/>
+      <c r="O34" s="40"/>
+      <c r="P34" s="41"/>
+      <c r="Q34" s="41"/>
+      <c r="R34" s="42"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -12543,10 +12543,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="39"/>
-      <c r="P35" s="40"/>
-      <c r="Q35" s="40"/>
-      <c r="R35" s="41"/>
+      <c r="O35" s="40"/>
+      <c r="P35" s="41"/>
+      <c r="Q35" s="41"/>
+      <c r="R35" s="42"/>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -12563,10 +12563,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="39"/>
-      <c r="P36" s="40"/>
-      <c r="Q36" s="40"/>
-      <c r="R36" s="41"/>
+      <c r="O36" s="40"/>
+      <c r="P36" s="41"/>
+      <c r="Q36" s="41"/>
+      <c r="R36" s="42"/>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -12583,10 +12583,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="39"/>
-      <c r="P37" s="40"/>
-      <c r="Q37" s="40"/>
-      <c r="R37" s="41"/>
+      <c r="O37" s="40"/>
+      <c r="P37" s="41"/>
+      <c r="Q37" s="41"/>
+      <c r="R37" s="42"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -12603,10 +12603,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="39"/>
-      <c r="P38" s="40"/>
-      <c r="Q38" s="40"/>
-      <c r="R38" s="41"/>
+      <c r="O38" s="40"/>
+      <c r="P38" s="41"/>
+      <c r="Q38" s="41"/>
+      <c r="R38" s="42"/>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -12623,10 +12623,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="39"/>
-      <c r="P39" s="40"/>
-      <c r="Q39" s="40"/>
-      <c r="R39" s="41"/>
+      <c r="O39" s="40"/>
+      <c r="P39" s="41"/>
+      <c r="Q39" s="41"/>
+      <c r="R39" s="42"/>
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -12643,10 +12643,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="39"/>
-      <c r="P40" s="40"/>
-      <c r="Q40" s="40"/>
-      <c r="R40" s="41"/>
+      <c r="O40" s="40"/>
+      <c r="P40" s="41"/>
+      <c r="Q40" s="41"/>
+      <c r="R40" s="42"/>
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -12663,10 +12663,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="40"/>
-      <c r="Q41" s="40"/>
-      <c r="R41" s="41"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="41"/>
+      <c r="Q41" s="41"/>
+      <c r="R41" s="42"/>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -12683,10 +12683,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="39"/>
-      <c r="P42" s="40"/>
-      <c r="Q42" s="40"/>
-      <c r="R42" s="41"/>
+      <c r="O42" s="40"/>
+      <c r="P42" s="41"/>
+      <c r="Q42" s="41"/>
+      <c r="R42" s="42"/>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -12703,10 +12703,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="39"/>
-      <c r="P43" s="40"/>
-      <c r="Q43" s="40"/>
-      <c r="R43" s="41"/>
+      <c r="O43" s="40"/>
+      <c r="P43" s="41"/>
+      <c r="Q43" s="41"/>
+      <c r="R43" s="42"/>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -12723,10 +12723,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="39"/>
-      <c r="P44" s="40"/>
-      <c r="Q44" s="40"/>
-      <c r="R44" s="41"/>
+      <c r="O44" s="40"/>
+      <c r="P44" s="41"/>
+      <c r="Q44" s="41"/>
+      <c r="R44" s="42"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -13556,32 +13556,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="3" priority="1">
@@ -13619,23 +13619,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="34" t="s">
+      <c r="M2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -13648,14 +13648,14 @@
         <f>SUM(Tabla115[Importa])</f>
         <v>0</v>
       </c>
-      <c r="M3" s="37" t="s">
+      <c r="M3" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="37"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="37"/>
-      <c r="R3" s="37"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -13686,12 +13686,12 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="M4" s="36"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18" t="str">
@@ -13706,21 +13706,21 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J5" s="38" t="s">
+      <c r="J5" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="38"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
+      <c r="K5" s="25"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C6" t="str">
         <f t="shared" si="0"/>
@@ -13730,19 +13730,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C7" t="str">
         <f t="shared" si="0"/>
@@ -13752,19 +13752,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="36"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C8" t="str">
         <f t="shared" si="0"/>
@@ -13774,19 +13774,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="36"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C9" t="str">
         <f t="shared" si="0"/>
@@ -13796,19 +13796,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C10" t="str">
         <f t="shared" si="0"/>
@@ -13818,19 +13818,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="36"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C11" t="str">
         <f t="shared" si="0"/>
@@ -13840,19 +13840,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C12" t="str">
         <f t="shared" si="0"/>
@@ -13862,19 +13862,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C13" t="str">
         <f t="shared" si="0"/>
@@ -13884,19 +13884,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C14" t="str">
         <f t="shared" si="0"/>
@@ -13906,19 +13906,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J14" s="38"/>
-      <c r="K14" s="38"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="36"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="36"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C15" t="str">
         <f t="shared" si="0"/>
@@ -13928,17 +13928,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="36"/>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="36"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46088.795299189813</v>
+        <v>46091.79682546296</v>
       </c>
       <c r="C16" t="str">
         <f t="shared" si="0"/>
@@ -13948,12 +13948,12 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="36"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18" t="str">
@@ -13968,12 +13968,12 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="36"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18" t="str">
@@ -13988,12 +13988,12 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="36"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18" t="str">
@@ -14008,12 +14008,12 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="36"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="23"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18" t="str">
@@ -14028,12 +14028,12 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M20" s="36"/>
-      <c r="N20" s="36"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="36"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
+      <c r="O20" s="23"/>
+      <c r="P20" s="23"/>
+      <c r="Q20" s="23"/>
+      <c r="R20" s="23"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18" t="str">
@@ -14048,12 +14048,12 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="36"/>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="36"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="23"/>
+      <c r="O21" s="23"/>
+      <c r="P21" s="23"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="str">
@@ -14068,12 +14068,12 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="36"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="str">
@@ -14102,14 +14102,14 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="32" t="s">
+      <c r="M24" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="42"/>
-      <c r="O24" s="42"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="42"/>
-      <c r="R24" s="42"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="39"/>
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="str">
@@ -14124,12 +14124,12 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="37"/>
-      <c r="N25" s="37"/>
-      <c r="O25" s="37"/>
-      <c r="P25" s="37"/>
-      <c r="Q25" s="37"/>
-      <c r="R25" s="37"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="24"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18" t="str">
@@ -14150,12 +14150,12 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="31" t="s">
+      <c r="O26" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
     </row>
     <row r="27" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18" t="str">
@@ -14172,10 +14172,10 @@
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="15"/>
-      <c r="O27" s="39"/>
-      <c r="P27" s="40"/>
-      <c r="Q27" s="40"/>
-      <c r="R27" s="41"/>
+      <c r="O27" s="40"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="42"/>
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="str">
@@ -14192,10 +14192,10 @@
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="40"/>
-      <c r="Q28" s="40"/>
-      <c r="R28" s="41"/>
+      <c r="O28" s="40"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="42"/>
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="str">
@@ -14212,10 +14212,10 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="40"/>
-      <c r="Q29" s="40"/>
-      <c r="R29" s="41"/>
+      <c r="O29" s="40"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="42"/>
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -14232,10 +14232,10 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="40"/>
-      <c r="Q30" s="40"/>
-      <c r="R30" s="41"/>
+      <c r="O30" s="40"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="42"/>
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -14252,10 +14252,10 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="39"/>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="40"/>
-      <c r="R31" s="41"/>
+      <c r="O31" s="40"/>
+      <c r="P31" s="41"/>
+      <c r="Q31" s="41"/>
+      <c r="R31" s="42"/>
     </row>
     <row r="32" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -14272,10 +14272,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="39"/>
-      <c r="P32" s="40"/>
-      <c r="Q32" s="40"/>
-      <c r="R32" s="41"/>
+      <c r="O32" s="40"/>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="41"/>
+      <c r="R32" s="42"/>
     </row>
     <row r="33" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -14292,10 +14292,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="39"/>
-      <c r="P33" s="40"/>
-      <c r="Q33" s="40"/>
-      <c r="R33" s="41"/>
+      <c r="O33" s="40"/>
+      <c r="P33" s="41"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="42"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -14312,10 +14312,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="39"/>
-      <c r="P34" s="40"/>
-      <c r="Q34" s="40"/>
-      <c r="R34" s="41"/>
+      <c r="O34" s="40"/>
+      <c r="P34" s="41"/>
+      <c r="Q34" s="41"/>
+      <c r="R34" s="42"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -14332,10 +14332,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="39"/>
-      <c r="P35" s="40"/>
-      <c r="Q35" s="40"/>
-      <c r="R35" s="41"/>
+      <c r="O35" s="40"/>
+      <c r="P35" s="41"/>
+      <c r="Q35" s="41"/>
+      <c r="R35" s="42"/>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -14352,10 +14352,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="39"/>
-      <c r="P36" s="40"/>
-      <c r="Q36" s="40"/>
-      <c r="R36" s="41"/>
+      <c r="O36" s="40"/>
+      <c r="P36" s="41"/>
+      <c r="Q36" s="41"/>
+      <c r="R36" s="42"/>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -14372,10 +14372,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="39"/>
-      <c r="P37" s="40"/>
-      <c r="Q37" s="40"/>
-      <c r="R37" s="41"/>
+      <c r="O37" s="40"/>
+      <c r="P37" s="41"/>
+      <c r="Q37" s="41"/>
+      <c r="R37" s="42"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -14392,10 +14392,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="39"/>
-      <c r="P38" s="40"/>
-      <c r="Q38" s="40"/>
-      <c r="R38" s="41"/>
+      <c r="O38" s="40"/>
+      <c r="P38" s="41"/>
+      <c r="Q38" s="41"/>
+      <c r="R38" s="42"/>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -14412,10 +14412,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="39"/>
-      <c r="P39" s="40"/>
-      <c r="Q39" s="40"/>
-      <c r="R39" s="41"/>
+      <c r="O39" s="40"/>
+      <c r="P39" s="41"/>
+      <c r="Q39" s="41"/>
+      <c r="R39" s="42"/>
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -14432,10 +14432,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="39"/>
-      <c r="P40" s="40"/>
-      <c r="Q40" s="40"/>
-      <c r="R40" s="41"/>
+      <c r="O40" s="40"/>
+      <c r="P40" s="41"/>
+      <c r="Q40" s="41"/>
+      <c r="R40" s="42"/>
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -14452,10 +14452,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="40"/>
-      <c r="Q41" s="40"/>
-      <c r="R41" s="41"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="41"/>
+      <c r="Q41" s="41"/>
+      <c r="R41" s="42"/>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -14472,10 +14472,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="39"/>
-      <c r="P42" s="40"/>
-      <c r="Q42" s="40"/>
-      <c r="R42" s="41"/>
+      <c r="O42" s="40"/>
+      <c r="P42" s="41"/>
+      <c r="Q42" s="41"/>
+      <c r="R42" s="42"/>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -14492,10 +14492,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="39"/>
-      <c r="P43" s="40"/>
-      <c r="Q43" s="40"/>
-      <c r="R43" s="41"/>
+      <c r="O43" s="40"/>
+      <c r="P43" s="41"/>
+      <c r="Q43" s="41"/>
+      <c r="R43" s="42"/>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -14512,10 +14512,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="39"/>
-      <c r="P44" s="40"/>
-      <c r="Q44" s="40"/>
-      <c r="R44" s="41"/>
+      <c r="O44" s="40"/>
+      <c r="P44" s="41"/>
+      <c r="Q44" s="41"/>
+      <c r="R44" s="42"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -15345,32 +15345,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="1" priority="1">
